--- a/data/trans_camb/IMC_inf_MED_R3-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R3-Habitat-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-2.139981840560934</v>
+        <v>-1.246880033916983</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-11.2426856938851</v>
+        <v>-11.11398910845769</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-2.290681539408484</v>
+        <v>-5.181934526018075</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-2.828747356708722</v>
+        <v>-2.789252098301914</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-2.130445373933015</v>
+        <v>-3.00273216843466</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-7.26415487137912</v>
+        <v>-7.222499125008469</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-12.50324605502339</v>
+        <v>-12.38483124786262</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-22.74010239605436</v>
+        <v>-20.79721341574579</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-11.98026895898505</v>
+        <v>-13.60597375092762</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-12.66389748126523</v>
+        <v>-12.95879677095262</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-9.401102294734834</v>
+        <v>-9.703127311217967</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-15.63462949626259</v>
+        <v>-14.32927098535878</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7.3349742945113</v>
+        <v>7.588655897979753</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.09038773199533716</v>
+        <v>-0.03701565281258151</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6.886151950469108</v>
+        <v>3.061575110758331</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>8.622649190720487</v>
+        <v>7.687272281607288</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>5.615223395848639</v>
+        <v>3.3082132869745</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5692468120883134</v>
+        <v>0.2016843066334852</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.0777511627914198</v>
+        <v>-0.04771730176189672</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.4084763099526575</v>
+        <v>-0.4253252579566274</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.1119181342904442</v>
+        <v>-0.2534637128595127</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1382069576653668</v>
+        <v>-0.136430552988875</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.0882945825499989</v>
+        <v>-0.1285157855041763</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.3010570136153731</v>
+        <v>-0.3091201933063405</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.398972074356264</v>
+        <v>-0.3973206942297342</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.6912160172166085</v>
+        <v>-0.6979269268550693</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.4851739265021526</v>
+        <v>-0.5593730725339364</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.5263048621808251</v>
+        <v>-0.5517960875081674</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3458040870705267</v>
+        <v>-0.3681537834231448</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.5563354582054776</v>
+        <v>-0.5477068070665765</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.3205642051487008</v>
+        <v>0.3769092640132489</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.04161066569055581</v>
+        <v>0.04137422148325204</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.4381169858244667</v>
+        <v>0.2163428547495852</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.5360614925549463</v>
+        <v>0.4607143404317345</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2738839391270937</v>
+        <v>0.1649900902104664</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.03395677377347802</v>
+        <v>0.01215640844144552</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-9.293204257341955</v>
+        <v>-8.58900539454568</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-1.583696355231817</v>
+        <v>-1.097473537015392</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-9.696609441453358</v>
+        <v>-8.773148037366491</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-9.638775196915002</v>
+        <v>-7.265101147938447</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-9.590938375402891</v>
+        <v>-8.672684407814499</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-3.929193642026879</v>
+        <v>-2.603586188728502</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-17.40423861611197</v>
+        <v>-15.92322625285024</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-11.45585363218875</v>
+        <v>-9.972989785986028</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-16.15765618986672</v>
+        <v>-14.11949901093065</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-17.16205329217399</v>
+        <v>-14.09821642816106</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-14.89770888535316</v>
+        <v>-13.45973214130089</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-10.30846239120797</v>
+        <v>-8.602215139023583</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-1.291851976797347</v>
+        <v>-2.247499597597494</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>8.59518286686848</v>
+        <v>8.187581475366464</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-3.16458026136474</v>
+        <v>-4.060782160698192</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-1.641559713047681</v>
+        <v>0.5920562841890349</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-5.067563744589822</v>
+        <v>-4.004406064282173</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>2.857566299749398</v>
+        <v>4.076959476128978</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.3196684284458138</v>
+        <v>-0.3119377379182146</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.05447612158232259</v>
+        <v>-0.03985833013669819</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.5019229768279114</v>
+        <v>-0.5040398800660915</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.4989293184407655</v>
+        <v>-0.4173987143130599</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.3929124712487995</v>
+        <v>-0.3831479457964192</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.1609674802898522</v>
+        <v>-0.1150230601054048</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.5185442566874816</v>
+        <v>-0.5083710161355199</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.3526381253970389</v>
+        <v>-0.3195124698994334</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.69169268903504</v>
+        <v>-0.6774553779458301</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.7652289982042061</v>
+        <v>-0.7051240166113993</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5396871447244121</v>
+        <v>-0.5400015587220062</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.390927532367832</v>
+        <v>-0.3548317183097857</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.04729876239366064</v>
+        <v>-0.09976366969413174</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.3210564013369581</v>
+        <v>0.3323183950770982</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.2169328752401347</v>
+        <v>-0.2478507865400364</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.05487905923144859</v>
+        <v>0.07393135638034168</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.2223100761192515</v>
+        <v>-0.2017550702417273</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.1273253734500252</v>
+        <v>0.2049747590250168</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-9.50110506304862</v>
+        <v>-6.402466865946188</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-17.96758231396499</v>
+        <v>-13.58301054341579</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-10.51285358790112</v>
+        <v>-10.78115369580285</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-15.79955048011043</v>
+        <v>-14.83940350445186</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-9.90661387786902</v>
+        <v>-8.472680922948273</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-16.70450704042985</v>
+        <v>-14.11880719348703</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-18.98403662553057</v>
+        <v>-14.91853122921995</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-27.51428865835956</v>
+        <v>-22.2020370801975</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-18.70659670081034</v>
+        <v>-18.64606601600445</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-23.7732467248269</v>
+        <v>-23.38341421930707</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-16.43337007509793</v>
+        <v>-13.89707536341661</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-23.16191975345878</v>
+        <v>-20.55562462419033</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>-0.3160265687870243</v>
+        <v>1.921274462560381</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-7.22775258693289</v>
+        <v>-3.207120121321636</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-2.500200939260934</v>
+        <v>-3.173592276680058</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-5.191346077126119</v>
+        <v>-4.51347737895518</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-3.312078620739691</v>
+        <v>-2.643953558649897</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-8.470032589406703</v>
+        <v>-7.128414866895789</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.3021754380109076</v>
+        <v>-0.2382488933151839</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.5714453234324395</v>
+        <v>-0.5054516169493732</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.4028006827800945</v>
+        <v>-0.4142957534855566</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.605360824993438</v>
+        <v>-0.5702452659168097</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.3442336410270193</v>
+        <v>-0.3202168273442371</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.5804458870587942</v>
+        <v>-0.5336067398853718</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.5212434749398657</v>
+        <v>-0.4826007722492547</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.7651803686730652</v>
+        <v>-0.745940529556371</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.615218555391399</v>
+        <v>-0.6052275690184502</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.823564947941374</v>
+        <v>-0.7971724028146083</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.5030020875281187</v>
+        <v>-0.4648193003453784</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.7357995755391924</v>
+        <v>-0.7095209395074883</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.00228128597499597</v>
+        <v>0.0875050754652416</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-0.2436833270407184</v>
+        <v>-0.1191670517395211</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-0.1070876658345052</v>
+        <v>-0.1335491158181155</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.214839618880051</v>
+        <v>-0.1767339506032467</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.1323041772632939</v>
+        <v>-0.1086708749683661</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.3090115739748861</v>
+        <v>-0.2872976436732146</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-4.464568442377298</v>
+        <v>-4.621526961029085</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-6.754654257225651</v>
+        <v>-5.536280561812728</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-7.314371774582276</v>
+        <v>-7.777887940646314</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-10.47584944170861</v>
+        <v>-10.69251816172167</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-5.787112816992576</v>
+        <v>-6.110877247324161</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-8.751901903727461</v>
+        <v>-8.225597547348137</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-12.61350615939152</v>
+        <v>-11.69948992870681</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-17.08920656250813</v>
+        <v>-14.74220790735089</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-14.74637685949857</v>
+        <v>-14.90916827349492</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-18.98469038895708</v>
+        <v>-18.34449654104649</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-11.34574080534614</v>
+        <v>-11.24825496016155</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-15.2728903029487</v>
+        <v>-14.50907760971005</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3.368633854378595</v>
+        <v>2.026608433597683</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4.390335879954457</v>
+        <v>4.696220694697193</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.7079422226138428</v>
+        <v>-0.7321897476785661</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-1.792223609790746</v>
+        <v>-1.827320754101726</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.3010331767467634</v>
+        <v>-0.8758513012228032</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-1.175369352280621</v>
+        <v>-1.692366057995857</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.1802492004302524</v>
+        <v>-0.2013968601401211</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.2727074396466004</v>
+        <v>-0.2412599842878753</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.3358645222142458</v>
+        <v>-0.3634678742980429</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.4810346364611439</v>
+        <v>-0.49967123167517</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2485952616808757</v>
+        <v>-0.2754879113697151</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.3759528132187221</v>
+        <v>-0.3708228125641129</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.4309375945990169</v>
+        <v>-0.4454182245555274</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.6003820256948026</v>
+        <v>-0.5680167729462454</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.5724249732605182</v>
+        <v>-0.5986384124725597</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.7516422580781424</v>
+        <v>-0.7457526127383342</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.4297745962447648</v>
+        <v>-0.4485992101719538</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.5988524126221888</v>
+        <v>-0.5864205456825933</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.1672243257938789</v>
+        <v>0.1048567943053485</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.2084632405043745</v>
+        <v>0.2417128624293223</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.0545520916331072</v>
+        <v>-0.03116434695755184</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.08210224832446217</v>
+        <v>-0.06629559523205869</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.01303913831363416</v>
+        <v>-0.04423534627440955</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.05415637232768289</v>
+        <v>-0.07327907825894393</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-6.598248158520778</v>
+        <v>-5.583151166360387</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-8.113762417935517</v>
+        <v>-6.68556263533474</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-7.893069262130526</v>
+        <v>-8.197869741194271</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-10.11183936014612</v>
+        <v>-9.143744298366643</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-7.176371486902122</v>
+        <v>-6.782909945409507</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-8.722738741024012</v>
+        <v>-7.573650100786969</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-11.03258844248462</v>
+        <v>-9.284304315577327</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-12.91320251250455</v>
+        <v>-11.84553850774274</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-11.27482969603891</v>
+        <v>-11.71637426954293</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-14.10600311865373</v>
+        <v>-12.98082423588392</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-9.892999748091762</v>
+        <v>-9.331034448888031</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-12.1826609401635</v>
+        <v>-10.70824123917432</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-2.142384736099197</v>
+        <v>-1.727670538408725</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-2.543874511370215</v>
+        <v>-1.845889933489961</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-3.426379899764664</v>
+        <v>-4.734638920651528</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-4.807337501895701</v>
+        <v>-4.459975793351885</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-3.951096404486645</v>
+        <v>-4.039963180515583</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-5.004738583199533</v>
+        <v>-4.243707485344875</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.2350514343468103</v>
+        <v>-0.2159870972607307</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2890390674109686</v>
+        <v>-0.2586344564447968</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.3618655677473216</v>
+        <v>-0.3899495765883395</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.4635872775860201</v>
+        <v>-0.4349421654826973</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.2869308769885928</v>
+        <v>-0.2886984772911741</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.3487588513599657</v>
+        <v>-0.3223544568969415</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.354259004094362</v>
+        <v>-0.3396624314896944</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.4393574037103257</v>
+        <v>-0.4281998567625147</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.4813608701542939</v>
+        <v>-0.5075838240134847</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.6060895617186332</v>
+        <v>-0.5883578104932133</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.3768725029847597</v>
+        <v>-0.3794695429892992</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.4610866861073419</v>
+        <v>-0.4351962147731114</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.07647618632731647</v>
+        <v>-0.07210510242710264</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-0.09703842434576994</v>
+        <v>-0.07156923439645424</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.1825640570666804</v>
+        <v>-0.2474241005013212</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.2439439414312926</v>
+        <v>-0.2333212092101253</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.1701161162912276</v>
+        <v>-0.1806509855487162</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.2107793357035836</v>
+        <v>-0.1880863014103842</v>
       </c>
     </row>
     <row r="34">
